--- a/engineer_forms/030_television_broadcasting_engineer_job_application--engineer_forms.xlsx
+++ b/engineer_forms/030_television_broadcasting_engineer_job_application--engineer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -677,8 +677,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'high_school',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'High School', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_"bachelor's_degree",_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': "Bachelor's Degree", 'label': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_"master's_degree",_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': "Master's Degree", 'label': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'doctoral_degree',_'label':_'doctoral_degree'}</t>
+          <t>doctoral_degree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Doctoral Degree', 'label': 'Doctoral Degree'}</t>
+          <t>Doctoral Degree</t>
         </is>
       </c>
     </row>
